--- a/doc/install-package/群众信息模板.xlsx
+++ b/doc/install-package/群众信息模板.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27531"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27726"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\poor\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspace\RuoYi-Vue\doc\install-package\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2440E462-E5E7-4604-85F8-35343462D5A8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6FC68EE5-ACF1-499D-8126-186CEDB33551}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="20445" yWindow="3285" windowWidth="25530" windowHeight="17355" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="315" yWindow="2670" windowWidth="26715" windowHeight="15435" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,24 +25,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="9">
   <si>
     <t>身份证号</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>371426198911237000</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>371426198911237001</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>371426198911237002</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>姓名</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -72,45 +60,6 @@
   </si>
   <si>
     <t>详细地址</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>张三</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>李四</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>王五</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>男</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>女</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>是</t>
-  </si>
-  <si>
-    <t>是</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>否</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>也一样</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">SDFSD </t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -457,7 +406,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I4"/>
+  <dimension ref="A1:I1"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="27.125" style="1" customWidth="1"/>
@@ -472,115 +421,31 @@
   <sheetData>
     <row r="1" spans="1:9" s="3" customFormat="1" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="B1" s="4" t="s">
         <v>0</v>
       </c>
       <c r="C1" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="D1" s="5" t="s">
+      <c r="G1" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="H1" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="F1" s="4" t="s">
+      <c r="I1" s="3" t="s">
         <v>8</v>
-      </c>
-      <c r="G1" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="H1" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="I1" s="3" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A2" t="s">
-        <v>12</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C2" t="s">
-        <v>15</v>
-      </c>
-      <c r="D2" s="2">
-        <v>32865</v>
-      </c>
-      <c r="E2" t="s">
-        <v>18</v>
-      </c>
-      <c r="F2" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="G2" t="s">
-        <v>18</v>
-      </c>
-      <c r="H2">
-        <v>15650019763</v>
-      </c>
-      <c r="I2" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A3" t="s">
-        <v>13</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="C3" t="s">
-        <v>16</v>
-      </c>
-      <c r="D3" s="2">
-        <v>32866</v>
-      </c>
-      <c r="E3" t="s">
-        <v>17</v>
-      </c>
-      <c r="F3" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="G3" t="s">
-        <v>18</v>
-      </c>
-      <c r="H3">
-        <v>15650019764</v>
-      </c>
-      <c r="I3" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A4" t="s">
-        <v>14</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="C4" t="s">
-        <v>15</v>
-      </c>
-      <c r="D4" s="2">
-        <v>36517</v>
-      </c>
-      <c r="E4" t="s">
-        <v>19</v>
-      </c>
-      <c r="G4" t="s">
-        <v>19</v>
-      </c>
-      <c r="H4">
-        <v>15650019765</v>
-      </c>
-      <c r="I4" t="s">
-        <v>21</v>
       </c>
     </row>
   </sheetData>
